--- a/chapter1_Getting Started/ADSP_계산문제.xlsx
+++ b/chapter1_Getting Started/ADSP_계산문제.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__OpenSolver__" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -11067,7 +11068,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>100</v>
       </c>
       <c r="B2" s="1" t="n">
@@ -11082,11 +11083,11 @@
         <v/>
       </c>
       <c r="E2" s="1">
-        <f>C2^2</f>
+        <f>POWER(C2,2)</f>
         <v/>
       </c>
       <c r="F2" s="1">
-        <f>D2^2</f>
+        <f>POWER(D2,2)</f>
         <v/>
       </c>
       <c r="G2" s="2">
@@ -11099,7 +11100,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>305</v>
       </c>
       <c r="B3" s="1" t="n">
@@ -11114,11 +11115,11 @@
         <v/>
       </c>
       <c r="E3" s="1">
-        <f>C3^2</f>
+        <f>POWER(C3,2)</f>
         <v/>
       </c>
       <c r="F3" s="1">
-        <f>D3^2</f>
+        <f>POWER(D3,2)</f>
         <v/>
       </c>
       <c r="G3" s="2">
@@ -11131,7 +11132,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>579</v>
       </c>
       <c r="B4" s="1" t="n">
@@ -11146,11 +11147,11 @@
         <v/>
       </c>
       <c r="E4" s="1">
-        <f>C4^2</f>
+        <f>POWER(C4,2)</f>
         <v/>
       </c>
       <c r="F4" s="1">
-        <f>D4^2</f>
+        <f>POWER(D4,2)</f>
         <v/>
       </c>
       <c r="G4" s="2">
@@ -11163,7 +11164,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>730</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -11178,11 +11179,11 @@
         <v/>
       </c>
       <c r="E5" s="1">
-        <f>C5^2</f>
+        <f>POWER(C5,2)</f>
         <v/>
       </c>
       <c r="F5" s="1">
-        <f>D5^2</f>
+        <f>POWER(D5,2)</f>
         <v/>
       </c>
       <c r="G5" s="2">
@@ -11195,7 +11196,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>981</v>
       </c>
       <c r="B6" s="1" t="n">
@@ -11210,11 +11211,11 @@
         <v/>
       </c>
       <c r="E6" s="1">
-        <f>C6^2</f>
+        <f>POWER(C6,2)</f>
         <v/>
       </c>
       <c r="F6" s="1">
-        <f>D6^2</f>
+        <f>POWER(D6,2)</f>
         <v/>
       </c>
       <c r="G6" s="2">
@@ -11227,7 +11228,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>1139</v>
       </c>
       <c r="B7" s="1" t="n">
@@ -11242,11 +11243,11 @@
         <v/>
       </c>
       <c r="E7" s="1">
-        <f>C7^2</f>
+        <f>POWER(C7,2)</f>
         <v/>
       </c>
       <c r="F7" s="1">
-        <f>D7^2</f>
+        <f>POWER(D7,2)</f>
         <v/>
       </c>
       <c r="G7" s="2">
@@ -11259,7 +11260,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>1305</v>
       </c>
       <c r="B8" s="1" t="n">
@@ -11274,11 +11275,11 @@
         <v/>
       </c>
       <c r="E8" s="1">
-        <f>C8^2</f>
+        <f>POWER(C8,2)</f>
         <v/>
       </c>
       <c r="F8" s="1">
-        <f>D8^2</f>
+        <f>POWER(D8,2)</f>
         <v/>
       </c>
       <c r="G8" s="2">
@@ -11291,7 +11292,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>1555</v>
       </c>
       <c r="B9" s="1" t="n">
@@ -11306,11 +11307,11 @@
         <v/>
       </c>
       <c r="E9" s="1">
-        <f>C9^2</f>
+        <f>POWER(C9,2)</f>
         <v/>
       </c>
       <c r="F9" s="1">
-        <f>D9^2</f>
+        <f>POWER(D9,2)</f>
         <v/>
       </c>
       <c r="G9" s="2">
@@ -11323,7 +11324,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>1708</v>
       </c>
       <c r="B10" s="1" t="n">
@@ -11338,11 +11339,11 @@
         <v/>
       </c>
       <c r="E10" s="1">
-        <f>C10^2</f>
+        <f>POWER(C10,2)</f>
         <v/>
       </c>
       <c r="F10" s="1">
-        <f>D10^2</f>
+        <f>POWER(D10,2)</f>
         <v/>
       </c>
       <c r="G10" s="2">
@@ -11355,7 +11356,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>1918</v>
       </c>
       <c r="B11" s="1" t="n">
@@ -11370,11 +11371,11 @@
         <v/>
       </c>
       <c r="E11" s="1">
-        <f>C11^2</f>
+        <f>POWER(C11,2)</f>
         <v/>
       </c>
       <c r="F11" s="1">
-        <f>D11^2</f>
+        <f>POWER(D11,2)</f>
         <v/>
       </c>
       <c r="G11" s="2">
@@ -11387,7 +11388,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>2128</v>
       </c>
       <c r="B12" s="1" t="n">
@@ -11402,11 +11403,11 @@
         <v/>
       </c>
       <c r="E12" s="1">
-        <f>C12^2</f>
+        <f>POWER(C12,2)</f>
         <v/>
       </c>
       <c r="F12" s="1">
-        <f>D12^2</f>
+        <f>POWER(D12,2)</f>
         <v/>
       </c>
       <c r="G12" s="2">
@@ -11419,7 +11420,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>2344</v>
       </c>
       <c r="B13" s="1" t="n">
@@ -11434,11 +11435,11 @@
         <v/>
       </c>
       <c r="E13" s="1">
-        <f>C13^2</f>
+        <f>POWER(C13,2)</f>
         <v/>
       </c>
       <c r="F13" s="1">
-        <f>D13^2</f>
+        <f>POWER(D13,2)</f>
         <v/>
       </c>
       <c r="G13" s="2">
@@ -11451,7 +11452,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>2638</v>
       </c>
       <c r="B14" s="1" t="n">
@@ -11466,11 +11467,11 @@
         <v/>
       </c>
       <c r="E14" s="1">
-        <f>C14^2</f>
+        <f>POWER(C14,2)</f>
         <v/>
       </c>
       <c r="F14" s="1">
-        <f>D14^2</f>
+        <f>POWER(D14,2)</f>
         <v/>
       </c>
       <c r="G14" s="2">
@@ -11483,7 +11484,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>2936</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -11498,11 +11499,11 @@
         <v/>
       </c>
       <c r="E15" s="1">
-        <f>C15^2</f>
+        <f>POWER(C15,2)</f>
         <v/>
       </c>
       <c r="F15" s="1">
-        <f>D15^2</f>
+        <f>POWER(D15,2)</f>
         <v/>
       </c>
       <c r="G15" s="2">
@@ -11515,7 +11516,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>3120</v>
       </c>
       <c r="B16" s="1" t="n">
@@ -11530,11 +11531,11 @@
         <v/>
       </c>
       <c r="E16" s="1">
-        <f>C16^2</f>
+        <f>POWER(C16,2)</f>
         <v/>
       </c>
       <c r="F16" s="1">
-        <f>D16^2</f>
+        <f>POWER(D16,2)</f>
         <v/>
       </c>
       <c r="G16" s="2">
@@ -11547,7 +11548,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>3342</v>
       </c>
       <c r="B17" s="1" t="n">
@@ -11562,11 +11563,11 @@
         <v/>
       </c>
       <c r="E17" s="1">
-        <f>C17^2</f>
+        <f>POWER(C17,2)</f>
         <v/>
       </c>
       <c r="F17" s="1">
-        <f>D17^2</f>
+        <f>POWER(D17,2)</f>
         <v/>
       </c>
       <c r="G17" s="2">
@@ -11579,7 +11580,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>1031284.07</v>
       </c>
       <c r="B18" s="1" t="n">
@@ -11594,11 +11595,11 @@
         <v/>
       </c>
       <c r="E18" s="1">
-        <f>C18^2</f>
+        <f>POWER(C18,2)</f>
         <v/>
       </c>
       <c r="F18" s="1">
-        <f>D18^2</f>
+        <f>POWER(D18,2)</f>
         <v/>
       </c>
       <c r="G18" s="2">
@@ -14302,7 +14303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14348,7 +14349,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14360,7 +14360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14382,7 +14382,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
